--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_until_2004_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_until_2004_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,61 +441,61 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>30.27076575999998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,33 +506,33 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>30.27076575999999</v>
       </c>
       <c r="G2" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>30.27076575999999</v>
       </c>
       <c r="I2" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>30.27076575999998</v>
       </c>
       <c r="K2" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>174.8695282133332</v>
+        <v>243.6040990933333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,33 +543,33 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="F3" t="n">
-        <v>174.8695282133333</v>
+        <v>209.5404933577774</v>
       </c>
       <c r="G3" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="H3" t="n">
-        <v>174.8695282133332</v>
+        <v>209.5404933577774</v>
       </c>
       <c r="I3" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="J3" t="n">
-        <v>174.8695282133332</v>
+        <v>240.3333093701463</v>
       </c>
       <c r="K3" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>200.5228515922441</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,33 +580,33 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="F4" t="n">
-        <v>200.5228515922441</v>
+        <v>245.3832345504309</v>
       </c>
       <c r="G4" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="H4" t="n">
-        <v>200.5228515922441</v>
+        <v>248.8726666112772</v>
       </c>
       <c r="I4" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="J4" t="n">
-        <v>200.5228515922441</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="K4" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>240.3924605609872</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,33 +617,33 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="F5" t="n">
-        <v>239.1861950852612</v>
+        <v>245.3832345504309</v>
       </c>
       <c r="G5" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="H5" t="n">
-        <v>243.8381316725355</v>
+        <v>248.8726666112771</v>
       </c>
       <c r="I5" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="J5" t="n">
-        <v>243.6040990933333</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="K5" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>240.3924605609872</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,29 +654,29 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="F6" t="n">
-        <v>239.1861950852612</v>
+        <v>245.3832345504309</v>
       </c>
       <c r="G6" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="H6" t="n">
-        <v>243.8381316725355</v>
+        <v>248.8726666112771</v>
       </c>
       <c r="I6" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
       <c r="J6" t="n">
-        <v>243.6040990933333</v>
+        <v>260.4893691686138</v>
       </c>
       <c r="K6" t="n">
-        <v>82556.26445685999</v>
+        <v>82607.53161779948</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -690,29 +691,29 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>123.83439668529</v>
+        <v>59.66674391264583</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>123.83439668529</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>59.62971406194096</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>59.62971406194096</v>
+        <v>59.66674391264583</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -727,29 +728,29 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>123.83439668529</v>
+        <v>84.98272644732454</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>123.83439668529</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>84.92998521382526</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>84.92998521382526</v>
+        <v>84.98272644732454</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -764,29 +765,29 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>123.83439668529</v>
+        <v>97.72408538642568</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>123.83439668529</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>97.66343672261678</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>97.66343672261678</v>
+        <v>97.72408538642568</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -801,29 +802,29 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>123.83439668529</v>
+        <v>104.9381294181997</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>123.83439668529</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>104.8730036377266</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>104.8730036377266</v>
+        <v>104.9381294181997</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -838,33 +839,33 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>123.83439668529</v>
+        <v>109.3906381366368</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>123.83439668529</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>109.3227490792979</v>
+        <v>123.9112974266992</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>109.3227490792979</v>
+        <v>109.3906381366368</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02488834448941177</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,30 +879,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02488834448941177</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02488834448941177</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02488834448941177</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,30 +916,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02737681797227924</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02715092126117648</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1001,18 +1002,18 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02722203577166982</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02828220964705883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,30 +1027,30 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02715092126117648</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02745430609814417</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02828220964705883</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4039878199999999</v>
+        <v>0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1063,30 +1064,30 @@
         <v>4.0386995376</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4039878199999999</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4039878199999999</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4039878199999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>4.0386995376</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.764585993000001</v>
+        <v>0.3365966474453315</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,30 +1101,30 @@
         <v>4.0386995376</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7645859930000002</v>
+        <v>0.5195401574496002</v>
       </c>
       <c r="G18" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H18" t="n">
-        <v>0.764585993000001</v>
+        <v>0.518569599111063</v>
       </c>
       <c r="I18" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J18" t="n">
-        <v>0.764585993000001</v>
+        <v>0.3530422562600821</v>
       </c>
       <c r="K18" t="n">
         <v>4.0386995376</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.764585993000001</v>
+        <v>0.3365966474453315</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>4.0386995376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7645859930000002</v>
+        <v>0.5195401574496002</v>
       </c>
       <c r="G19" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H19" t="n">
-        <v>0.764585993000001</v>
+        <v>0.5185695991110632</v>
       </c>
       <c r="I19" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J19" t="n">
-        <v>0.764585993000001</v>
+        <v>0.3530422562600821</v>
       </c>
       <c r="K19" t="n">
         <v>4.0386995376</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.360598173000001</v>
+        <v>0.3365966474453315</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>4.0386995376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3605981730000002</v>
+        <v>0.5195401574496002</v>
       </c>
       <c r="G20" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H20" t="n">
-        <v>0.360598173000001</v>
+        <v>0.5185695991110632</v>
       </c>
       <c r="I20" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.360598173000001</v>
+        <v>0.3530422562600821</v>
       </c>
       <c r="K20" t="n">
         <v>4.0386995376</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.360598173000001</v>
+        <v>0.2403987820000005</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>4.0386995376</v>
       </c>
       <c r="F21" t="n">
-        <v>0.360598173000001</v>
+        <v>0.360598173</v>
       </c>
       <c r="G21" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H21" t="n">
-        <v>0.360598173000001</v>
+        <v>0.3283635340721826</v>
       </c>
       <c r="I21" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J21" t="n">
-        <v>0.360598173000001</v>
+        <v>0.2403987820000005</v>
       </c>
       <c r="K21" t="n">
         <v>4.0386995376</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,7 +1490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -1985,7 +1986,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>11.61716401549292</v>
+        <v>5.902980058762853</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1997,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>5.902980058762853</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2022,7 +2023,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>11.61716401549292</v>
+        <v>8.285549227162472</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2034,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>8.285549227162472</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2059,7 +2060,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>11.61716401549292</v>
+        <v>9.4400349268659</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2071,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>9.4400349268659</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2096,7 +2097,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>11.61716401549292</v>
+        <v>10.07480347185033</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2108,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>10.07480347185033</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2118,11 +2119,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>10.58136974085145</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2133,7 +2134,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>11.61716401549292</v>
+        <v>10.45758010009884</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2145,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.45758010009884</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2170,29 +2171,29 @@
         <v>0.08</v>
       </c>
       <c r="E47" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2207,33 +2208,33 @@
         <v>0.08</v>
       </c>
       <c r="E48" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1541442714345456</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2244,33 +2245,33 @@
         <v>0.08</v>
       </c>
       <c r="E49" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2460247381318316</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1516591621861038</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2202067600041814</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1541442714345456</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2281,33 +2282,33 @@
         <v>0.08</v>
       </c>
       <c r="E50" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2460247381318316</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1516591621861038</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2202067600041814</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1541442714345456</v>
+        <v>0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2318,33 +2319,33 @@
         <v>0.08</v>
       </c>
       <c r="E51" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2460247381318316</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1516591621861038</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2202067600041814</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1.196790377398138</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2355,33 +2356,33 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
-        <v>23.19492632776108</v>
+        <v>6.420410922853913</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1.219312947337952</v>
       </c>
       <c r="G52" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1.196790377398138</v>
       </c>
       <c r="I52" t="n">
-        <v>5.103403554063369</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1.219312947337952</v>
       </c>
       <c r="K52" t="n">
-        <v>5.103403554063369</v>
+        <v>6.420410922853913</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>2.39640127869907</v>
+        <v>4.581566613217581</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2392,33 +2393,33 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
-        <v>23.19492632776108</v>
+        <v>10.45583104262237</v>
       </c>
       <c r="F53" t="n">
-        <v>2.61184512152766</v>
+        <v>4.598517804163184</v>
       </c>
       <c r="G53" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H53" t="n">
-        <v>2.309810937968122</v>
+        <v>4.598517804163184</v>
       </c>
       <c r="I53" t="n">
-        <v>8.311045187725474</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J53" t="n">
-        <v>2.61184512152766</v>
+        <v>4.596898440045019</v>
       </c>
       <c r="K53" t="n">
-        <v>8.311045187725474</v>
+        <v>10.45583104262237</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>5.47936021200669</v>
+        <v>5.934376063209609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,33 +2430,33 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
-        <v>23.19492632776108</v>
+        <v>13.15855285087932</v>
       </c>
       <c r="F54" t="n">
-        <v>5.679093091668479</v>
+        <v>6.110909354494274</v>
       </c>
       <c r="G54" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H54" t="n">
-        <v>5.394940741083412</v>
+        <v>5.988829356447125</v>
       </c>
       <c r="I54" t="n">
-        <v>10.45936252249382</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J54" t="n">
-        <v>5.697885505739111</v>
+        <v>6.077418732837953</v>
       </c>
       <c r="K54" t="n">
-        <v>10.45936252249382</v>
+        <v>13.15855285087932</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.814033124984921</v>
+        <v>5.829231227829982</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,33 +2467,33 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
-        <v>23.19492632776108</v>
+        <v>15.06411707719942</v>
       </c>
       <c r="F55" t="n">
-        <v>6.039870020563401</v>
+        <v>5.911302518822621</v>
       </c>
       <c r="G55" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H55" t="n">
-        <v>5.726984817092851</v>
+        <v>5.875357997017567</v>
       </c>
       <c r="I55" t="n">
-        <v>11.97404177931236</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J55" t="n">
-        <v>6.044979073653214</v>
+        <v>5.83734065952648</v>
       </c>
       <c r="K55" t="n">
-        <v>11.97404177931236</v>
+        <v>15.06411707719942</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.987895714702679</v>
+        <v>5.829231227829982</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,29 +2504,29 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
-        <v>23.19492632776108</v>
+        <v>16.46376285834269</v>
       </c>
       <c r="F56" t="n">
-        <v>5.933856083482261</v>
+        <v>5.911302518822621</v>
       </c>
       <c r="G56" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H56" t="n">
-        <v>5.993358195931629</v>
+        <v>5.875357997017567</v>
       </c>
       <c r="I56" t="n">
-        <v>13.08658073355445</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J56" t="n">
-        <v>5.92905310495893</v>
+        <v>5.837340659526479</v>
       </c>
       <c r="K56" t="n">
-        <v>13.08658073355445</v>
+        <v>16.46376285834269</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,29 +2541,29 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
-        <v>23.19492632776108</v>
+        <v>6.420410922853913</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>5.103403554063369</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>5.103403554063369</v>
+        <v>6.420410922853913</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,29 +2578,29 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>23.19492632776108</v>
+        <v>10.45583104262237</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>8.311045187725474</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>8.311045187725474</v>
+        <v>10.45583104262237</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,29 +2615,29 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
-        <v>23.19492632776108</v>
+        <v>13.15855285087932</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>10.45936252249382</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>10.45936252249382</v>
+        <v>13.15855285087932</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,29 +2652,29 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
-        <v>23.19492632776108</v>
+        <v>15.06411707719942</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>11.97404177931236</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>11.97404177931236</v>
+        <v>15.06411707719942</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,29 +2689,29 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
-        <v>23.19492632776108</v>
+        <v>16.46376285834269</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>13.08658073355445</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>13.08658073355445</v>
+        <v>16.46376285834269</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2725,29 +2726,29 @@
         <v>0.08</v>
       </c>
       <c r="E62" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
@@ -2762,33 +2763,33 @@
         <v>0.08</v>
       </c>
       <c r="E63" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>2.937941786817327</v>
+        <v>2.249058300668978</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,33 +2800,33 @@
         <v>0.08</v>
       </c>
       <c r="E64" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F64" t="n">
-        <v>2.926323598807787</v>
+        <v>2.143335015407045</v>
       </c>
       <c r="G64" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H64" t="n">
-        <v>2.9382560262581</v>
+        <v>2.249058300668979</v>
       </c>
       <c r="I64" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J64" t="n">
-        <v>2.933349162864805</v>
+        <v>2.106015631040635</v>
       </c>
       <c r="K64" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>3.416380081798112</v>
+        <v>3.354203136048604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,33 +2837,33 @@
         <v>0.08</v>
       </c>
       <c r="E65" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F65" t="n">
-        <v>3.384312247289346</v>
+        <v>3.342941851078698</v>
       </c>
       <c r="G65" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H65" t="n">
-        <v>3.403171574872295</v>
+        <v>3.362529660098537</v>
       </c>
       <c r="I65" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J65" t="n">
-        <v>3.384312247289347</v>
+        <v>3.346093704352108</v>
       </c>
       <c r="K65" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>3.676656921864435</v>
+        <v>3.354203136048604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,29 +2874,29 @@
         <v>0.08</v>
       </c>
       <c r="E66" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F66" t="n">
-        <v>3.736350922502318</v>
+        <v>3.342941851078698</v>
       </c>
       <c r="G66" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H66" t="n">
-        <v>3.655042857300103</v>
+        <v>3.362529660098537</v>
       </c>
       <c r="I66" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J66" t="n">
-        <v>3.720444975987811</v>
+        <v>3.346093704352108</v>
       </c>
       <c r="K66" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2910,29 +2911,29 @@
         <v>0.08</v>
       </c>
       <c r="E67" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2947,29 +2948,29 @@
         <v>0.08</v>
       </c>
       <c r="E68" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -2984,29 +2985,29 @@
         <v>0.08</v>
       </c>
       <c r="E69" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3021,29 +3022,29 @@
         <v>0.08</v>
       </c>
       <c r="E70" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3058,29 +3059,29 @@
         <v>0.08</v>
       </c>
       <c r="E71" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,29 +3096,29 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>23.19492632776108</v>
+        <v>1.786539916583664</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1.420070190104964</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1.420070190104964</v>
+        <v>1.786539916583664</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,29 +3133,29 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>23.19492632776108</v>
+        <v>3.186881113320015</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2.533161910587705</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>2.533161910587705</v>
+        <v>3.186881113320015</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,29 +3170,29 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>23.19492632776108</v>
+        <v>4.327835376387487</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>3.440074273538773</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>3.440074273538773</v>
+        <v>4.327835376387487</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,29 +3207,29 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>23.19492632776108</v>
+        <v>5.284112711597216</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>4.200192155372148</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>4.200192155372148</v>
+        <v>5.284112711597216</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,29 +3244,29 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>23.19492632776108</v>
+        <v>6.101277553742589</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>4.849733440154369</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>4.849733440154369</v>
+        <v>6.101277553742589</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3280,33 +3281,33 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>23.19492632776108</v>
+        <v>1.786539916583664</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1.420070190104964</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1.420070190104964</v>
+        <v>1.786539916583664</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2799951583495339</v>
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3317,33 +3318,33 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>23.19492632776108</v>
+        <v>3.186881113320015</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H78" t="n">
-        <v>0.366585499080483</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2.533161910587705</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>2.533161910587705</v>
+        <v>3.186881113320015</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.2799951583495339</v>
+        <v>0</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3354,33 +3355,33 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>23.19492632776108</v>
+        <v>4.327835376387487</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H79" t="n">
-        <v>0.366585499080483</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>3.440074273538773</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>3.440074273538773</v>
+        <v>4.327835376387487</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
-        <v>0.2799951583495339</v>
+        <v>0</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3391,29 +3392,29 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>23.19492632776108</v>
+        <v>5.284112711597216</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H80" t="n">
-        <v>0.366585499080483</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>4.200192155372148</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>4.200192155372148</v>
+        <v>5.284112711597216</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,29 +3429,29 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>23.19492632776108</v>
+        <v>6.101277553742589</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>23.19492632776108</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>4.849733440154369</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>4.849733440154369</v>
+        <v>6.101277553742589</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3463,7 +3464,7 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3475,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3485,7 +3486,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3498,7 +3499,7 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -3510,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3520,7 +3521,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3533,7 +3534,7 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -3545,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3555,7 +3556,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3568,7 +3569,7 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -3580,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3590,7 +3591,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3603,7 +3604,7 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3615,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3625,7 +3626,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3638,7 +3639,7 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -3650,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3660,7 +3661,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3673,7 +3674,7 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -3685,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3695,7 +3696,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3708,7 +3709,7 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -3720,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3730,7 +3731,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3743,7 +3744,7 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -3755,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3765,7 +3766,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3778,7 +3779,7 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -3790,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3800,7 +3801,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3813,7 +3814,7 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.2712070570783821</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3825,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2712070570783821</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3835,7 +3836,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3848,7 +3849,7 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>0.4370978189737727</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3860,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4370978189737727</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3870,7 +3871,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3883,7 +3884,7 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.5456964388783678</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3895,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5456964388783678</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3905,7 +3906,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3918,7 +3919,7 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0.6207578627767205</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3930,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6207578627767205</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3940,7 +3941,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
@@ -3953,7 +3954,7 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0.6749874416447547</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -3965,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6749874416447547</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>

--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_until_2004_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_until_2004_investment_decision.xlsx
@@ -441,52 +441,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>30.27076575999998</v>
+        <v>55.86502570689592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>82607.53161779948</v>
       </c>
       <c r="F2" t="n">
-        <v>30.27076575999999</v>
+        <v>54.19327854256254</v>
       </c>
       <c r="G2" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="H2" t="n">
-        <v>30.27076575999999</v>
+        <v>55.86502570689592</v>
       </c>
       <c r="I2" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="J2" t="n">
-        <v>30.27076575999998</v>
+        <v>53.62934503153134</v>
       </c>
       <c r="K2" t="n">
         <v>82607.53161779948</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>243.6040990933333</v>
+        <v>153.5760053860492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>82607.53161779948</v>
       </c>
       <c r="F3" t="n">
-        <v>209.5404933577774</v>
+        <v>156.6685702088214</v>
       </c>
       <c r="G3" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="H3" t="n">
-        <v>209.5404933577774</v>
+        <v>156.6685702088213</v>
       </c>
       <c r="I3" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="J3" t="n">
-        <v>240.3333093701463</v>
+        <v>156.2322539769068</v>
       </c>
       <c r="K3" t="n">
         <v>82607.53161779948</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>260.4893691686138</v>
+        <v>153.5760053860492</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>82607.53161779948</v>
       </c>
       <c r="F4" t="n">
-        <v>245.3832345504309</v>
+        <v>158.9853940883791</v>
       </c>
       <c r="G4" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="H4" t="n">
-        <v>248.8726666112772</v>
+        <v>156.6685702088213</v>
       </c>
       <c r="I4" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="J4" t="n">
-        <v>260.4893691686138</v>
+        <v>156.2322539769068</v>
       </c>
       <c r="K4" t="n">
         <v>82607.53161779948</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>260.4893691686138</v>
+        <v>153.5760053860492</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>82607.53161779948</v>
       </c>
       <c r="F5" t="n">
-        <v>245.3832345504309</v>
+        <v>158.9853940883791</v>
       </c>
       <c r="G5" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="H5" t="n">
-        <v>248.8726666112771</v>
+        <v>156.6685702088213</v>
       </c>
       <c r="I5" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="J5" t="n">
-        <v>260.4893691686138</v>
+        <v>156.2322539769068</v>
       </c>
       <c r="K5" t="n">
         <v>82607.53161779948</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>260.4893691686138</v>
+        <v>153.5760053860492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>82607.53161779948</v>
       </c>
       <c r="F6" t="n">
-        <v>245.3832345504309</v>
+        <v>158.9853940883791</v>
       </c>
       <c r="G6" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="H6" t="n">
-        <v>248.8726666112771</v>
+        <v>156.6685702088213</v>
       </c>
       <c r="I6" t="n">
         <v>82607.53161779948</v>
       </c>
       <c r="J6" t="n">
-        <v>260.4893691686138</v>
+        <v>156.2322539769068</v>
       </c>
       <c r="K6" t="n">
         <v>82607.53161779948</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>59.66674391264583</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>123.9112974266992</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>123.9112974266992</v>
+        <v>0.3126585862876939</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>59.66674391264583</v>
+        <v>0.3126585862876939</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>84.98272644732454</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>123.9112974266992</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>123.9112974266992</v>
+        <v>0.4453163918043617</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>84.98272644732454</v>
+        <v>0.4453163918043617</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>97.72408538642568</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>123.9112974266992</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>123.9112974266992</v>
+        <v>0.5120821479367175</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>97.72408538642568</v>
+        <v>0.5120821479367175</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>104.9381294181997</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>123.9112974266992</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>123.9112974266992</v>
+        <v>0.5498843248360272</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>104.9381294181997</v>
+        <v>0.5498843248360272</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_until_2004</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>109.3906381366368</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>123.9112974266992</v>
+        <v>0.6493052668539323</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>123.9112974266992</v>
+        <v>0.5732158323065583</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>109.3906381366368</v>
+        <v>0.5732158323065583</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02049418451281925</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02049418451281925</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.02103085840241832</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02601963287529412</v>
+        <v>0.020699511199028</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02488834448941177</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02488834448941177</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02505514200829523</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02488834448941176</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02511310325368664</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02505335257387175</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02505514200829522</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02488834448941176</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02737681797227924</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02715092126117647</v>
+        <v>0.02505514200829523</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02722203577166982</v>
+        <v>0.02488834448941176</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02828220964705883</v>
+        <v>0.02715092126117647</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02715092126117648</v>
+        <v>0.02601963287529412</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02745430609814417</v>
+        <v>0.02505514200829523</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02828220964705883</v>
+        <v>0.02488834448941177</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3365966474453315</v>
+        <v>1.367564791316225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>4.0386995376</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5195401574496002</v>
+        <v>1.356866972688008</v>
       </c>
       <c r="G18" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H18" t="n">
-        <v>0.518569599111063</v>
+        <v>1.30502254164004</v>
       </c>
       <c r="I18" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3530422562600821</v>
+        <v>1.304116150004221</v>
       </c>
       <c r="K18" t="n">
         <v>4.0386995376</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3365966474453315</v>
+        <v>1.375747027834693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>4.0386995376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5195401574496002</v>
+        <v>1.356866972688008</v>
       </c>
       <c r="G19" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5185695991110632</v>
+        <v>1.30502254164004</v>
       </c>
       <c r="I19" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3530422562600821</v>
+        <v>1.304116150004221</v>
       </c>
       <c r="K19" t="n">
         <v>4.0386995376</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3365966474453315</v>
+        <v>1.375747027834693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>4.0386995376</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5195401574496002</v>
+        <v>1.356866972688008</v>
       </c>
       <c r="G20" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5185695991110632</v>
+        <v>1.30502254164004</v>
       </c>
       <c r="I20" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3530422562600821</v>
+        <v>1.304116150004221</v>
       </c>
       <c r="K20" t="n">
         <v>4.0386995376</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2403987820000005</v>
+        <v>1.321642186543719</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>4.0386995376</v>
       </c>
       <c r="F21" t="n">
-        <v>0.360598173</v>
+        <v>1.322193301</v>
       </c>
       <c r="G21" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3283635340721826</v>
+        <v>1.28804663115484</v>
       </c>
       <c r="I21" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2403987820000005</v>
+        <v>1.28949332607102</v>
       </c>
       <c r="K21" t="n">
         <v>4.0386995376</v>
@@ -1477,13 +1477,13 @@
         <v>4.0386995376</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.03619897404563798</v>
       </c>
       <c r="I28" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.03868326406552802</v>
       </c>
       <c r="K28" t="n">
         <v>4.0386995376</v>
@@ -1514,13 +1514,13 @@
         <v>4.0386995376</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.05993069828041295</v>
       </c>
       <c r="I29" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.06235993750091215</v>
       </c>
       <c r="K29" t="n">
         <v>4.0386995376</v>
@@ -1551,13 +1551,13 @@
         <v>4.0386995376</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.0599306982804129</v>
       </c>
       <c r="I30" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.06235993750091214</v>
       </c>
       <c r="K30" t="n">
         <v>4.0386995376</v>
@@ -1588,13 +1588,13 @@
         <v>4.0386995376</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.02373172423477497</v>
       </c>
       <c r="I31" t="n">
         <v>4.0386995376</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.02367667343538411</v>
       </c>
       <c r="K31" t="n">
         <v>4.0386995376</v>
@@ -1986,7 +1986,7 @@
         <v>0.03</v>
       </c>
       <c r="E42" t="n">
-        <v>5.902980058762853</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>11.61716401549292</v>
+        <v>5.902980058762853</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>0.03</v>
       </c>
       <c r="E43" t="n">
-        <v>8.285549227162472</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>11.61716401549292</v>
+        <v>8.285549227162472</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0.03</v>
       </c>
       <c r="E44" t="n">
-        <v>9.4400349268659</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>11.61716401549292</v>
+        <v>9.4400349268659</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>0.03</v>
       </c>
       <c r="E45" t="n">
-        <v>10.07480347185033</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>11.61716401549292</v>
+        <v>10.07480347185033</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>10.58136974085145</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>0.03</v>
       </c>
       <c r="E46" t="n">
-        <v>10.45758010009884</v>
+        <v>11.61716401549292</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2146,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>11.61716401549292</v>
+        <v>10.45758010009884</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>10.58136974085145</v>
       </c>
       <c r="K46" t="n">
         <v>10.45758010009884</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>1.196790377398138</v>
+        <v>1.197618123837952</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2356,22 +2356,22 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.168934350220313</v>
+      </c>
+      <c r="G52" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.197618123837952</v>
+      </c>
+      <c r="I52" t="n">
         <v>6.420410922853913</v>
       </c>
-      <c r="F52" t="n">
-        <v>1.219312947337952</v>
-      </c>
-      <c r="G52" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1.196790377398138</v>
-      </c>
-      <c r="I52" t="n">
-        <v>29.18071376718328</v>
-      </c>
       <c r="J52" t="n">
-        <v>1.219312947337952</v>
+        <v>1.168490252580376</v>
       </c>
       <c r="K52" t="n">
         <v>6.420410922853913</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>4.581566613217581</v>
+        <v>4.510542289102074</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2393,22 +2393,22 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4.49220390946694</v>
+      </c>
+      <c r="G53" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.49220390946694</v>
+      </c>
+      <c r="I53" t="n">
         <v>10.45583104262237</v>
       </c>
-      <c r="F53" t="n">
-        <v>4.598517804163184</v>
-      </c>
-      <c r="G53" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H53" t="n">
-        <v>4.598517804163184</v>
-      </c>
-      <c r="I53" t="n">
-        <v>29.18071376718328</v>
-      </c>
       <c r="J53" t="n">
-        <v>4.596898440045019</v>
+        <v>4.489273029921089</v>
       </c>
       <c r="K53" t="n">
         <v>10.45583104262237</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>5.934376063209609</v>
+        <v>5.980340789548718</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2430,22 +2430,22 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.895180163036366</v>
+      </c>
+      <c r="G54" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H54" t="n">
+        <v>5.911841706860169</v>
+      </c>
+      <c r="I54" t="n">
         <v>13.15855285087932</v>
       </c>
-      <c r="F54" t="n">
-        <v>6.110909354494274</v>
-      </c>
-      <c r="G54" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H54" t="n">
-        <v>5.988829356447125</v>
-      </c>
-      <c r="I54" t="n">
-        <v>29.18071376718328</v>
-      </c>
       <c r="J54" t="n">
-        <v>6.077418732837953</v>
+        <v>5.914979494796154</v>
       </c>
       <c r="K54" t="n">
         <v>13.15855285087932</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.829231227829982</v>
+        <v>5.934082026798688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2467,22 +2467,22 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.867748276401471</v>
+      </c>
+      <c r="G55" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.650426529495826</v>
+      </c>
+      <c r="I55" t="n">
         <v>15.06411707719942</v>
       </c>
-      <c r="F55" t="n">
-        <v>5.911302518822621</v>
-      </c>
-      <c r="G55" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H55" t="n">
-        <v>5.875357997017567</v>
-      </c>
-      <c r="I55" t="n">
-        <v>29.18071376718328</v>
-      </c>
       <c r="J55" t="n">
-        <v>5.83734065952648</v>
+        <v>5.57857948601251</v>
       </c>
       <c r="K55" t="n">
         <v>15.06411707719942</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.829231227829982</v>
+        <v>5.934082026798687</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2504,22 +2504,22 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.867748276401469</v>
+      </c>
+      <c r="G56" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5.661263137956391</v>
+      </c>
+      <c r="I56" t="n">
         <v>16.46376285834269</v>
       </c>
-      <c r="F56" t="n">
-        <v>5.911302518822621</v>
-      </c>
-      <c r="G56" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H56" t="n">
-        <v>5.875357997017567</v>
-      </c>
-      <c r="I56" t="n">
-        <v>29.18071376718328</v>
-      </c>
       <c r="J56" t="n">
-        <v>5.837340659526479</v>
+        <v>5.592056894876851</v>
       </c>
       <c r="K56" t="n">
         <v>16.46376285834269</v>
@@ -2541,19 +2541,19 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>6.420410922853913</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>29.18071376718328</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2578,19 +2578,19 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>10.45583104262237</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>29.18071376718328</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2615,19 +2615,19 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>13.15855285087932</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>29.18071376718328</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2652,19 +2652,19 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>15.06411707719942</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>29.18071376718328</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2689,19 +2689,19 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>29.18071376718328</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>16.46376285834269</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>29.18071376718328</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>29.18071376718328</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>2.249058300668978</v>
+        <v>0.5660728102773274</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>29.18071376718328</v>
       </c>
       <c r="F64" t="n">
-        <v>2.143335015407045</v>
+        <v>0.6541628540913846</v>
       </c>
       <c r="G64" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="H64" t="n">
-        <v>2.249058300668979</v>
+        <v>0.6178048299735381</v>
       </c>
       <c r="I64" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="J64" t="n">
-        <v>2.106015631040635</v>
+        <v>0.6298484174219335</v>
       </c>
       <c r="K64" t="n">
         <v>29.18071376718328</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>3.354203136048604</v>
+        <v>1.517574142734392</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>29.18071376718328</v>
       </c>
       <c r="F65" t="n">
-        <v>3.342941851078698</v>
+        <v>1.577388948588611</v>
       </c>
       <c r="G65" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="H65" t="n">
-        <v>3.362529660098537</v>
+        <v>1.828683977129306</v>
       </c>
       <c r="I65" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="J65" t="n">
-        <v>3.346093704352108</v>
+        <v>1.901406798484362</v>
       </c>
       <c r="K65" t="n">
         <v>29.18071376718328</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>3.354203136048604</v>
+        <v>1.517574142734392</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>29.18071376718328</v>
       </c>
       <c r="F66" t="n">
-        <v>3.342941851078698</v>
+        <v>1.577388948588611</v>
       </c>
       <c r="G66" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="H66" t="n">
-        <v>3.362529660098537</v>
+        <v>1.828683977129306</v>
       </c>
       <c r="I66" t="n">
         <v>29.18071376718328</v>
       </c>
       <c r="J66" t="n">
-        <v>3.346093704352108</v>
+        <v>1.901406798484362</v>
       </c>
       <c r="K66" t="n">
         <v>29.18071376718328</v>
@@ -3096,7 +3096,7 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>1.786539916583664</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1.786539916583664</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="73">
@@ -3133,7 +3133,7 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>3.186881113320015</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>3.186881113320015</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="74">
@@ -3170,7 +3170,7 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>4.327835376387487</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>4.327835376387487</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="75">
@@ -3207,7 +3207,7 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>5.284112711597216</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>5.284112711597216</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="76">
@@ -3244,7 +3244,7 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>6.101277553742589</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>6.101277553742589</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="77">
@@ -3281,7 +3281,7 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>1.786539916583664</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1.786539916583664</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="78">
@@ -3318,7 +3318,7 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>3.186881113320015</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>3.186881113320015</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="79">
@@ -3355,7 +3355,7 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>4.327835376387487</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>4.327835376387487</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="80">
@@ -3392,7 +3392,7 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>5.284112711597216</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>5.284112711597216</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="81">
@@ -3429,7 +3429,7 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>6.101277553742589</v>
+        <v>29.18071376718328</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>6.101277553742589</v>
+        <v>29.18071376718328</v>
       </c>
     </row>
     <row r="82">
@@ -3464,19 +3464,19 @@
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3499,19 +3499,19 @@
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3569,19 +3569,19 @@
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3604,19 +3604,19 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3639,19 +3639,19 @@
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3674,19 +3674,19 @@
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3709,19 +3709,19 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3744,19 +3744,19 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3779,19 +3779,19 @@
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3814,19 +3814,19 @@
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.2712070570783821</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3849,19 +3849,19 @@
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.4370978189737727</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3884,19 +3884,19 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.5456964388783678</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3919,19 +3919,19 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6207578627767205</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3954,19 +3954,19 @@
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6749874416447547</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
